--- a/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.10.xlsx
+++ b/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.10.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">rand</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4 mins</t>
+    <t xml:space="preserve">5.2 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.051</v>
+        <v>0.0481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055</v>
+        <v>0.0454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0514</v>
+        <v>0.0474</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0537</v>
+        <v>0.0461</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0518</v>
+        <v>0.0452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0528</v>
+        <v>0.0475</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.0494</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.0543</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.0568</v>
+        <v>0.052</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0512</v>
+        <v>0.0475</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0492</v>
+        <v>0.0438</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0521</v>
+        <v>0.0453</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
